--- a/templates/consolidated-data-sample-template.xlsx
+++ b/templates/consolidated-data-sample-template.xlsx
@@ -5,24 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Documents\arbaiza-consulting\environmental-sensor-poc\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bryce\Documents\arbaiza\environmental-sensor-poc\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217B9B1-D15B-41AA-B533-B489882749FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EE61AB-A012-4DED-88C6-A9E2890CC4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="devices" sheetId="1" r:id="rId1"/>
-    <sheet name="sensors" sheetId="2" r:id="rId2"/>
-    <sheet name="device_readings_daily" sheetId="4" r:id="rId3"/>
-    <sheet name="device_readings_last1000" sheetId="5" r:id="rId4"/>
+    <sheet name="notes" sheetId="6" r:id="rId1"/>
+    <sheet name="devices" sheetId="1" r:id="rId2"/>
+    <sheet name="sensors" sheetId="2" r:id="rId3"/>
+    <sheet name="device_readings_daily" sheetId="4" r:id="rId4"/>
+    <sheet name="device_readings_last1000" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">device_readings_daily!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">device_readings_last1000!$A$1:$K$1001</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">devices!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">sensors!$A$1:$E$398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">device_readings_daily!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">device_readings_last1000!$A$1:$K$1001</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">devices!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">sensors!$A$1:$E$398</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>Source</t>
   </si>
@@ -103,6 +104,36 @@
   </si>
   <si>
     <t>SensorReadingRh</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>devices</t>
+  </si>
+  <si>
+    <t>sensors</t>
+  </si>
+  <si>
+    <t>device_readings_daily</t>
+  </si>
+  <si>
+    <t>device_readings_last1000</t>
+  </si>
+  <si>
+    <t>Full devices table from devices.parquet.</t>
+  </si>
+  <si>
+    <t>Full sensors table from sensors.parquet.</t>
+  </si>
+  <si>
+    <t>Full cubed data from device_readings_daily.parquet. For data query examples, see experiments/2-examples-analysis.ipynb.</t>
+  </si>
+  <si>
+    <t>First 500 and last 500 records from device_readings.parquet.</t>
   </si>
 </sst>
 </file>
@@ -433,18 +464,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D79762A-225E-48ED-9AF4-CC82963956B0}">
+  <dimension ref="B2:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.6328125" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
-    <col min="4" max="5" width="50.77734375" customWidth="1"/>
-    <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6328125" customWidth="1"/>
+    <col min="4" max="5" width="50.81640625" customWidth="1"/>
+    <col min="6" max="6" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,19 +556,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04DE2CC4-DFC8-4699-B107-22BCD5E3F531}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="4" max="4" width="34.08984375" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,24 +591,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE9CDF7-6F1F-4351-825F-A33B6933341C}">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.6328125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,24 +646,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B96A32-644B-4099-B29A-20EECE652D17}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" customWidth="1"/>
-    <col min="4" max="5" width="50.77734375" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.36328125" customWidth="1"/>
+    <col min="4" max="5" width="50.81640625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
